--- a/Participantes_Curso/E01/José María Benavente.xlsx
+++ b/Participantes_Curso/E01/José María Benavente.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="14655" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fase de Grupos" sheetId="1" state="visible" r:id="rId1"/>
@@ -173,26 +173,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -218,6 +198,26 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -237,6 +237,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
@@ -258,36 +279,15 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -655,7 +655,7 @@
       <c r="D3" s="20" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" thickBot="1">
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>España</t>
         </is>
@@ -1897,13 +1897,12 @@
   <mergeCells count="52">
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B98:D98"/>
     <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B98:D98"/>
-    <mergeCell ref="B48:D48"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B44:D44"/>
     <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B44:D44"/>
     <mergeCell ref="B78:D78"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
@@ -1913,25 +1912,26 @@
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B74:D74"/>
     <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B20:D20"/>
     <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B36:D36"/>
     <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B36:D36"/>
     <mergeCell ref="B76:D76"/>
     <mergeCell ref="B94:D94"/>
     <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B4:D4"/>
     <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B4:D4"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B100:D100"/>
     <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="B16:D16"/>
     <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B86:D86"/>
     <mergeCell ref="B72:D72"/>
     <mergeCell ref="B90:D90"/>
     <mergeCell ref="B3:D3"/>
@@ -1939,14 +1939,14 @@
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="B102:D102"/>
     <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B52:D52"/>
     <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B96:D96"/>
     <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B18:D18"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B48:D48"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B96 B100 B104" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
